--- a/12616112.xlsx
+++ b/12616112.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="573" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1202920-10FD-4613-A4D6-62980C3C051F}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80CAE25C-9F4A-4278-8A3B-402D13DDD203}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -216,34 +216,13 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>After coming home at 3.20 pm, giving tuitions feels like a hectic.</t>
-  </si>
-  <si>
-    <t>Felt happy because finally the weekend come.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>I helped my mother in home chores then and the whole day was relaxing.</t>
-  </si>
-  <si>
-    <t>I got a book of python issued from library and made some notes. Felt satisfied for trying.</t>
-  </si>
-  <si>
     <t>Going with the flow.</t>
   </si>
   <si>
     <t>I had enough time today to try something new.</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
   <si>
     <t>Started to work on patent. This is interesting.</t>
@@ -259,6 +238,9 @@
   </si>
   <si>
     <t>Today punjab was closed that is why I was unable to come to the university and hence I was so much worried about my attendance.</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
   <si>
     <t>After a long week, relaxed my mind from travelling daily.</t>
@@ -285,7 +267,13 @@
     <t>Felt happy that after a full 5 days of struggle, finally weekend arrive.</t>
   </si>
   <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
     <t>Took proper rest and care of myself.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
   <si>
     <t>Feeling energetic to give my best in the following week.</t>
@@ -1180,21 +1168,21 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="45.75">
+    <row r="7" spans="1:14" ht="15">
       <c r="A7" s="13">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B7" s="14">
         <v>360</v>
       </c>
       <c r="C7" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D7" s="14">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E7" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F7" s="14">
         <v>300</v>
@@ -1203,170 +1191,170 @@
         <v>6</v>
       </c>
       <c r="H7" s="14">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>990</v>
+        <f t="shared" ref="I7:I42" si="2">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>1000</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>450</v>
+        <f t="shared" ref="J7:J42" si="3">IF(I7="","",1440-I7)</f>
+        <v>440</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="30.75">
       <c r="A8" s="13">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="14">
         <v>390</v>
       </c>
       <c r="C8" s="14">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D8" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E8" s="14">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F8" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G8" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
+        <f t="shared" si="2"/>
+        <v>910</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f t="shared" si="3"/>
+        <v>530</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45.75">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="30.75">
       <c r="A9" s="13">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="14">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="C9" s="14">
         <v>60</v>
       </c>
       <c r="D9" s="14">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="E9" s="14">
-        <v>20</v>
-      </c>
-      <c r="F9" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="14">
+        <v>250</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14">
+        <v>130</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="shared" si="2"/>
+        <v>970</v>
+      </c>
+      <c r="J9" s="15">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="14">
+    </row>
+    <row r="10" spans="1:14" ht="30.75">
+      <c r="A10" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B10" s="14">
+        <v>360</v>
+      </c>
+      <c r="C10" s="14">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14">
+        <v>90</v>
+      </c>
+      <c r="E10" s="14">
+        <v>45</v>
+      </c>
+      <c r="F10" s="14">
         <v>300</v>
       </c>
-      <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45.75">
-      <c r="A10" s="13">
-        <v>46250</v>
-      </c>
-      <c r="B10" s="14">
-        <v>450</v>
-      </c>
-      <c r="C10" s="14">
-        <v>50</v>
-      </c>
-      <c r="D10" s="14">
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
         <v>120</v>
       </c>
-      <c r="E10" s="14">
-        <v>30</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="14">
-        <v>240</v>
-      </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>890</v>
+        <f t="shared" si="2"/>
+        <v>955</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>550</v>
+        <f t="shared" si="3"/>
+        <v>485</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="76.5">
       <c r="A11" s="13">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B11" s="14">
         <v>360</v>
@@ -1375,73 +1363,73 @@
         <v>45</v>
       </c>
       <c r="D11" s="14">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E11" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F11" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+        <f t="shared" si="2"/>
+        <v>885</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>440</v>
+        <f t="shared" si="3"/>
+        <v>555</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>57</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="30.75">
       <c r="A12" s="13">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="B12" s="14">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="C12" s="14">
+        <v>40</v>
+      </c>
+      <c r="D12" s="14">
+        <v>210</v>
+      </c>
+      <c r="E12" s="14">
         <v>50</v>
       </c>
-      <c r="D12" s="14">
-        <v>120</v>
-      </c>
-      <c r="E12" s="14">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14">
-        <v>200</v>
-      </c>
-      <c r="G12" s="14">
-        <v>4</v>
+      <c r="F12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H12" s="14">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>910</v>
+        <f t="shared" si="2"/>
+        <v>930</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>530</v>
+        <f t="shared" si="3"/>
+        <v>510</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>53</v>
@@ -1458,85 +1446,85 @@
     </row>
     <row r="13" spans="1:14" ht="30.75">
       <c r="A13" s="13">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="B13" s="14">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>240</v>
+      </c>
+      <c r="E13" s="14">
         <v>60</v>
       </c>
-      <c r="D13" s="14">
-        <v>100</v>
-      </c>
-      <c r="E13" s="14">
-        <v>40</v>
-      </c>
-      <c r="F13" s="14">
-        <v>250</v>
-      </c>
-      <c r="G13" s="14">
-        <v>5</v>
+      <c r="F13" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H13" s="14">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>970</v>
+        <f t="shared" si="2"/>
+        <v>960</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>470</v>
+        <f t="shared" si="3"/>
+        <v>480</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="30.75">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="60.75">
       <c r="A14" s="13">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B14" s="14">
         <v>360</v>
       </c>
       <c r="C14" s="14">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D14" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E14" s="14">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F14" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="G14" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>955</v>
+        <f t="shared" si="2"/>
+        <v>1005</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>485</v>
+        <f t="shared" si="3"/>
+        <v>435</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>57</v>
@@ -1545,372 +1533,372 @@
         <v>55</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="76.5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="45.75">
       <c r="A15" s="13">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B15" s="14">
+        <v>330</v>
+      </c>
+      <c r="C15" s="14">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
+        <v>50</v>
+      </c>
+      <c r="E15" s="14">
+        <v>45</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>120</v>
+      </c>
+      <c r="I15" s="15">
+        <f t="shared" si="2"/>
+        <v>815</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="3"/>
+        <v>625</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="45.75">
+      <c r="A16" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B16" s="14">
         <v>360</v>
-      </c>
-      <c r="C15" s="14">
-        <v>45</v>
-      </c>
-      <c r="D15" s="14">
-        <v>240</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>240</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>885</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>555</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="30.75">
-      <c r="A16" s="13">
-        <v>46256</v>
-      </c>
-      <c r="B16" s="14">
-        <v>450</v>
       </c>
       <c r="C16" s="14">
         <v>40</v>
       </c>
       <c r="D16" s="14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>150</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>930</v>
+        <f t="shared" si="2"/>
+        <v>880</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>510</v>
+        <f t="shared" si="3"/>
+        <v>560</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>55</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="30.75">
       <c r="A17" s="13">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D17" s="14">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
-      </c>
-      <c r="F17" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="14" t="s">
-        <v>61</v>
+        <v>40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f t="shared" si="2"/>
+        <v>965</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f t="shared" si="3"/>
+        <v>475</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="60.75">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="45.75">
       <c r="A18" s="13">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B18" s="14">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="C18" s="14">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D18" s="14">
         <v>60</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F18" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
+        <v>120</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="3"/>
+        <v>490</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="30.75">
+      <c r="A19" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B19" s="14">
+        <v>420</v>
+      </c>
+      <c r="C19" s="14">
+        <v>50</v>
+      </c>
+      <c r="D19" s="14">
         <v>150</v>
       </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>1005</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>435</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M18" s="16" t="s">
+      <c r="E19" s="14">
         <v>55</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="F19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="14">
+        <v>240</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="2"/>
+        <v>915</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="3"/>
+        <v>525</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="45.75">
-      <c r="A19" s="13">
-        <v>46259</v>
-      </c>
-      <c r="B19" s="14">
-        <v>330</v>
-      </c>
-      <c r="C19" s="14">
-        <v>20</v>
-      </c>
-      <c r="D19" s="14">
-        <v>50</v>
-      </c>
-      <c r="E19" s="14">
-        <v>45</v>
-      </c>
-      <c r="F19" s="14">
-        <v>250</v>
-      </c>
-      <c r="G19" s="14">
-        <v>5</v>
-      </c>
-      <c r="H19" s="14">
-        <v>120</v>
-      </c>
-      <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>815</v>
-      </c>
-      <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>625</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="45.75">
+    <row r="20" spans="1:14" ht="30.75">
       <c r="A20" s="13">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B20" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="C20" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D20" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E20" s="14">
         <v>60</v>
       </c>
-      <c r="F20" s="14">
-        <v>150</v>
-      </c>
-      <c r="G20" s="14">
-        <v>3</v>
+      <c r="F20" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H20" s="14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>880</v>
+        <f t="shared" si="2"/>
+        <v>960</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>560</v>
+        <f t="shared" si="3"/>
+        <v>480</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="30.75">
+    <row r="21" spans="1:14" ht="60.75">
       <c r="A21" s="13">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B21" s="14">
         <v>360</v>
       </c>
       <c r="C21" s="14">
+        <v>40</v>
+      </c>
+      <c r="D21" s="14">
         <v>45</v>
       </c>
-      <c r="D21" s="14">
-        <v>90</v>
-      </c>
       <c r="E21" s="14">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F21" s="14">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="G21" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H21" s="14">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>965</v>
+        <f t="shared" si="2"/>
+        <v>1020</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="1"/>
-        <v>475</v>
+        <f t="shared" si="3"/>
+        <v>420</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N21" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="45.75">
+    <row r="22" spans="1:14" ht="30.75">
       <c r="A22" s="13">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B22" s="14">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="C22" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D22" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="E22" s="14">
         <v>30</v>
       </c>
       <c r="F22" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>950</v>
+        <f t="shared" si="2"/>
+        <v>855</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>490</v>
+        <f t="shared" si="3"/>
+        <v>585</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N22" s="17" t="s">
         <v>80</v>
@@ -1918,10 +1906,10 @@
     </row>
     <row r="23" spans="1:14" ht="30.75">
       <c r="A23" s="13">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B23" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C23" s="14">
         <v>50</v>
@@ -1930,125 +1918,125 @@
         <v>150</v>
       </c>
       <c r="E23" s="14">
-        <v>55</v>
-      </c>
-      <c r="F23" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>61</v>
+        <v>100</v>
+      </c>
+      <c r="F23" s="14">
+        <v>150</v>
+      </c>
+      <c r="G23" s="14">
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="0"/>
-        <v>915</v>
+        <f t="shared" si="2"/>
+        <v>990</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="1"/>
-        <v>525</v>
+        <f t="shared" si="3"/>
+        <v>450</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N23" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="30.75">
+    <row r="24" spans="1:14" ht="15">
       <c r="A24" s="13">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B24" s="14">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="C24" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E24" s="14">
-        <v>60</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="14" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
       </c>
       <c r="H24" s="14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f t="shared" si="2"/>
+        <v>860</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f t="shared" si="3"/>
+        <v>580</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L24" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N24" s="17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="60.75">
+    <row r="25" spans="1:14" ht="30.75">
       <c r="A25" s="13">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="14">
         <v>360</v>
       </c>
       <c r="C25" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D25" s="14">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="E25" s="14">
         <v>25</v>
       </c>
       <c r="F25" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
+        <f t="shared" si="2"/>
+        <v>940</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f t="shared" si="3"/>
+        <v>500</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="N25" s="17" t="s">
         <v>83</v>
@@ -2056,91 +2044,91 @@
     </row>
     <row r="26" spans="1:14" ht="30.75">
       <c r="A26" s="13">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B26" s="14">
-        <v>330</v>
+        <v>420</v>
       </c>
       <c r="C26" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D26" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E26" s="14">
-        <v>30</v>
-      </c>
-      <c r="F26" s="14">
-        <v>250</v>
-      </c>
-      <c r="G26" s="14">
-        <v>5</v>
+        <v>50</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H26" s="14">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
-        <v>855</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="1"/>
-        <v>585</v>
+        <f t="shared" si="3"/>
+        <v>350</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L26" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M26" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N26" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="30.75">
+    <row r="27" spans="1:14" ht="45.75">
       <c r="A27" s="13">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="B27" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C27" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D27" s="14">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="E27" s="14">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>150</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H27" s="14">
-        <v>180</v>
+        <v>400</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="0"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>1160</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="1"/>
-        <v>450</v>
+        <f t="shared" si="3"/>
+        <v>280</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N27" s="17" t="s">
         <v>85</v>
@@ -2148,312 +2136,312 @@
     </row>
     <row r="28" spans="1:14" ht="15">
       <c r="A28" s="13">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B28" s="14">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C28" s="14">
         <v>40</v>
       </c>
       <c r="D28" s="14">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="E28" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H28" s="14">
         <v>120</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>860</v>
+        <f t="shared" si="2"/>
+        <v>970</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="1"/>
-        <v>580</v>
+        <f t="shared" si="3"/>
+        <v>470</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N28" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30.75">
+    <row r="29" spans="1:14" ht="45.75">
       <c r="A29" s="13">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B29" s="14">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C29" s="14">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D29" s="14">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E29" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H29" s="14">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>940</v>
+        <f t="shared" si="2"/>
+        <v>840</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="1"/>
-        <v>500</v>
+        <f t="shared" si="3"/>
+        <v>600</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N29" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="30.75">
+    <row r="30" spans="1:14" ht="76.5">
       <c r="A30" s="13">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B30" s="14">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="C30" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D30" s="14">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E30" s="14">
-        <v>50</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>61</v>
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>150</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3</v>
       </c>
       <c r="H30" s="14">
-        <v>360</v>
+        <v>220</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+        <f t="shared" si="2"/>
+        <v>1010</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="1"/>
-        <v>350</v>
+        <f t="shared" si="3"/>
+        <v>430</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>53</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N30" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="45.75">
+    <row r="31" spans="1:14" ht="60.75">
       <c r="A31" s="13">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="C31" s="14">
+        <v>45</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>20</v>
+      </c>
+      <c r="F31" s="14">
+        <v>250</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>150</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="2"/>
+        <v>915</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="3"/>
+        <v>525</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="16" t="s">
         <v>55</v>
-      </c>
-      <c r="D31" s="14">
-        <v>240</v>
-      </c>
-      <c r="E31" s="14">
-        <v>45</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H31" s="14">
-        <v>400</v>
-      </c>
-      <c r="I31" s="15">
-        <f t="shared" si="0"/>
-        <v>1160</v>
-      </c>
-      <c r="J31" s="15">
-        <f t="shared" si="1"/>
-        <v>280</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>58</v>
       </c>
       <c r="N31" s="17" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="15">
+    <row r="32" spans="1:14" ht="60.75">
       <c r="A32" s="13">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="14">
         <v>360</v>
       </c>
       <c r="C32" s="14">
+        <v>50</v>
+      </c>
+      <c r="D32" s="14">
         <v>40</v>
       </c>
-      <c r="D32" s="14">
-        <v>50</v>
-      </c>
       <c r="E32" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F32" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G32" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H32" s="14">
         <v>120</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="0"/>
-        <v>970</v>
+        <f t="shared" si="2"/>
+        <v>900</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="1"/>
-        <v>470</v>
+        <f t="shared" si="3"/>
+        <v>540</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N32" s="17" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="45.75">
+    <row r="33" spans="1:14" ht="30.75">
       <c r="A33" s="13">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="14">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="C33" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D33" s="14">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="E33" s="14">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H33" s="14">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="I33" s="15">
-        <f t="shared" si="0"/>
-        <v>840</v>
+        <f t="shared" si="2"/>
+        <v>990</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="1"/>
-        <v>600</v>
+        <f t="shared" si="3"/>
+        <v>450</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L33" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N33" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="76.5">
+    <row r="34" spans="1:14" ht="45.75">
       <c r="A34" s="13">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B34" s="14">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="C34" s="14">
         <v>40</v>
       </c>
       <c r="D34" s="14">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E34" s="14">
-        <v>30</v>
-      </c>
-      <c r="F34" s="14">
-        <v>150</v>
-      </c>
-      <c r="G34" s="14">
-        <v>3</v>
+        <v>45</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H34" s="14">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="0"/>
-        <v>1010</v>
+        <f t="shared" si="2"/>
+        <v>985</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="1"/>
-        <v>430</v>
+        <f t="shared" si="3"/>
+        <v>455</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>53</v>
@@ -2468,9 +2456,9 @@
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="60.75">
+    <row r="35" spans="1:14" ht="30.75">
       <c r="A35" s="13">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="14">
         <v>360</v>
@@ -2479,33 +2467,33 @@
         <v>45</v>
       </c>
       <c r="D35" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E35" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F35" s="14">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="G35" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H35" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="0"/>
-        <v>915</v>
+        <f t="shared" si="2"/>
+        <v>955</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="1"/>
-        <v>525</v>
+        <f t="shared" si="3"/>
+        <v>485</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L35" s="16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M35" s="16" t="s">
         <v>55</v>
@@ -2514,93 +2502,93 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="60.75">
+    <row r="36" spans="1:14" ht="45.75">
       <c r="A36" s="13">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B36" s="14">
         <v>360</v>
       </c>
       <c r="C36" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D36" s="14">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E36" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F36" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G36" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
+        <f t="shared" si="2"/>
+        <v>910</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="1"/>
-        <v>540</v>
+        <f t="shared" si="3"/>
+        <v>530</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="N36" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="30.75">
+    <row r="37" spans="1:14" ht="45.75">
       <c r="A37" s="13">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B37" s="14">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="C37" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D37" s="14">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E37" s="14">
         <v>40</v>
       </c>
-      <c r="F37" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>61</v>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
       </c>
       <c r="H37" s="14">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="0"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>955</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="1"/>
-        <v>450</v>
+        <f t="shared" si="3"/>
+        <v>485</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="N37" s="17" t="s">
         <v>95</v>
@@ -2608,42 +2596,42 @@
     </row>
     <row r="38" spans="1:14" ht="45.75">
       <c r="A38" s="13">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="B38" s="14">
-        <v>450</v>
+        <v>390</v>
       </c>
       <c r="C38" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
         <v>240</v>
       </c>
-      <c r="E38" s="14">
-        <v>45</v>
-      </c>
-      <c r="F38" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H38" s="14">
-        <v>210</v>
-      </c>
       <c r="I38" s="15">
-        <f t="shared" si="0"/>
-        <v>985</v>
+        <f t="shared" si="2"/>
+        <v>720</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="1"/>
-        <v>455</v>
+        <f t="shared" si="3"/>
+        <v>720</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M38" s="16" t="s">
         <v>55</v>
@@ -2652,9 +2640,9 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="30.75">
+    <row r="39" spans="1:14" ht="60.75">
       <c r="A39" s="13">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B39" s="14">
         <v>360</v>
@@ -2663,33 +2651,33 @@
         <v>45</v>
       </c>
       <c r="D39" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E39" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F39" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G39" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H39" s="14">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I39" s="15">
-        <f t="shared" si="0"/>
-        <v>955</v>
+        <f t="shared" si="2"/>
+        <v>995</v>
       </c>
       <c r="J39" s="15">
-        <f t="shared" si="1"/>
-        <v>485</v>
+        <f t="shared" si="3"/>
+        <v>445</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="M39" s="16" t="s">
         <v>55</v>
@@ -2698,47 +2686,47 @@
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="45.75">
+    <row r="40" spans="1:14" ht="91.5">
       <c r="A40" s="13">
-        <v>46280</v>
+        <v>46284</v>
       </c>
       <c r="B40" s="14">
-        <v>360</v>
+        <v>450</v>
       </c>
       <c r="C40" s="14">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
         <v>60</v>
       </c>
-      <c r="E40" s="14">
-        <v>35</v>
-      </c>
-      <c r="F40" s="14">
-        <v>250</v>
-      </c>
-      <c r="G40" s="14">
-        <v>5</v>
+      <c r="F40" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H40" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>910</v>
+        <f t="shared" si="2"/>
+        <v>800</v>
       </c>
       <c r="J40" s="15">
-        <f t="shared" si="1"/>
-        <v>530</v>
+        <f t="shared" si="3"/>
+        <v>640</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L40" s="16" t="s">
         <v>54</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N40" s="17" t="s">
         <v>98</v>
@@ -2746,13 +2734,13 @@
     </row>
     <row r="41" spans="1:14" ht="45.75">
       <c r="A41" s="13">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B41" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D41" s="14">
         <v>180</v>
@@ -2760,31 +2748,31 @@
       <c r="E41" s="14">
         <v>40</v>
       </c>
-      <c r="F41" s="14">
-        <v>150</v>
-      </c>
-      <c r="G41" s="14">
-        <v>3</v>
+      <c r="F41" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>66</v>
       </c>
       <c r="H41" s="14">
         <v>180</v>
       </c>
       <c r="I41" s="15">
-        <f t="shared" si="0"/>
-        <v>955</v>
+        <f t="shared" si="2"/>
+        <v>870</v>
       </c>
       <c r="J41" s="15">
-        <f t="shared" si="1"/>
-        <v>485</v>
+        <f t="shared" si="3"/>
+        <v>570</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="N41" s="17" t="s">
         <v>99</v>
@@ -2792,233 +2780,113 @@
     </row>
     <row r="42" spans="1:14" ht="45.75">
       <c r="A42" s="13">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B42" s="14">
         <v>390</v>
       </c>
       <c r="C42" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D42" s="14">
+        <v>35</v>
+      </c>
+      <c r="E42" s="14">
+        <v>15</v>
+      </c>
+      <c r="F42" s="14">
+        <v>400</v>
+      </c>
+      <c r="G42" s="14">
+        <v>8</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="2"/>
+        <v>1080</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M42" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="E42" s="14">
-        <v>0</v>
-      </c>
-      <c r="F42" s="14">
-        <v>0</v>
-      </c>
-      <c r="G42" s="14">
-        <v>0</v>
-      </c>
-      <c r="H42" s="14">
-        <v>240</v>
-      </c>
-      <c r="I42" s="15">
-        <f t="shared" si="0"/>
-        <v>720</v>
-      </c>
-      <c r="J42" s="15">
-        <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="K42" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L42" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M42" s="16" t="s">
-        <v>55</v>
       </c>
       <c r="N42" s="17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="60.75">
-      <c r="A43" s="13">
-        <v>46283</v>
-      </c>
-      <c r="B43" s="14">
-        <v>360</v>
-      </c>
-      <c r="C43" s="14">
-        <v>45</v>
-      </c>
-      <c r="D43" s="14">
-        <v>90</v>
-      </c>
-      <c r="E43" s="14">
-        <v>50</v>
-      </c>
-      <c r="F43" s="14">
-        <v>300</v>
-      </c>
-      <c r="G43" s="14">
-        <v>6</v>
-      </c>
-      <c r="H43" s="14">
-        <v>150</v>
-      </c>
-      <c r="I43" s="15">
-        <f t="shared" si="0"/>
-        <v>995</v>
-      </c>
-      <c r="J43" s="15">
-        <f t="shared" si="1"/>
-        <v>445</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N43" s="17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="91.5">
-      <c r="A44" s="13">
-        <v>46284</v>
-      </c>
-      <c r="B44" s="14">
-        <v>450</v>
-      </c>
-      <c r="C44" s="14">
-        <v>50</v>
-      </c>
-      <c r="D44" s="14">
-        <v>120</v>
-      </c>
-      <c r="E44" s="14">
-        <v>60</v>
-      </c>
-      <c r="F44" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G44" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H44" s="14">
-        <v>120</v>
-      </c>
-      <c r="I44" s="15">
-        <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="J44" s="15">
-        <f t="shared" si="1"/>
-        <v>640</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="45.75">
-      <c r="A45" s="13">
-        <v>46285</v>
-      </c>
-      <c r="B45" s="14">
-        <v>420</v>
-      </c>
-      <c r="C45" s="14">
-        <v>50</v>
-      </c>
-      <c r="D45" s="14">
-        <v>180</v>
-      </c>
-      <c r="E45" s="14">
-        <v>40</v>
-      </c>
-      <c r="F45" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G45" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="14">
-        <v>180</v>
-      </c>
-      <c r="I45" s="15">
-        <f t="shared" si="0"/>
-        <v>870</v>
-      </c>
-      <c r="J45" s="15">
-        <f t="shared" si="1"/>
-        <v>570</v>
-      </c>
-      <c r="K45" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L45" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="M45" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N45" s="17" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="45.75">
-      <c r="A46" s="13">
-        <v>46286</v>
-      </c>
-      <c r="B46" s="14">
-        <v>390</v>
-      </c>
-      <c r="C46" s="14">
-        <v>40</v>
-      </c>
-      <c r="D46" s="14">
-        <v>35</v>
-      </c>
-      <c r="E46" s="14">
-        <v>15</v>
-      </c>
-      <c r="F46" s="14">
-        <v>400</v>
-      </c>
-      <c r="G46" s="14">
-        <v>8</v>
-      </c>
-      <c r="H46" s="14">
-        <v>200</v>
-      </c>
-      <c r="I46" s="15">
-        <f t="shared" si="0"/>
-        <v>1080</v>
-      </c>
-      <c r="J46" s="15">
-        <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="K46" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="M46" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N46" s="17" t="s">
-        <v>104</v>
-      </c>
+    <row r="43" spans="1:14" ht="15">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
+    </row>
+    <row r="44" spans="1:14" ht="15">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
+    </row>
+    <row r="45" spans="1:14" ht="15">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
+    </row>
+    <row r="46" spans="1:14" ht="15">
+      <c r="A46" s="13"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="13"/>
@@ -3536,11 +3404,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3558,11 +3426,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3580,11 +3448,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3602,11 +3470,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3624,11 +3492,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3646,11 +3514,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3668,11 +3536,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3690,11 +3558,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3712,11 +3580,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3734,11 +3602,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3756,11 +3624,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3778,11 +3646,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3800,11 +3668,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3822,11 +3690,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3844,11 +3712,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3866,11 +3734,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3888,11 +3756,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3910,11 +3778,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3932,11 +3800,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3954,11 +3822,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3976,11 +3844,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3998,11 +3866,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4020,11 +3888,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4042,11 +3910,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4064,11 +3932,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4086,11 +3954,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4108,11 +3976,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4130,11 +3998,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4152,11 +4020,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4174,11 +4042,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4196,11 +4064,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4218,11 +4086,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4240,11 +4108,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4262,11 +4130,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4284,11 +4152,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4306,11 +4174,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4328,11 +4196,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4350,11 +4218,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4372,11 +4240,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4394,11 +4262,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4416,11 +4284,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4438,11 +4306,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4460,11 +4328,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4482,11 +4350,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4504,11 +4372,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4526,11 +4394,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4548,11 +4416,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4570,11 +4438,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4592,11 +4460,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4614,11 +4482,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4636,11 +4504,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4658,11 +4526,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4680,11 +4548,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4702,11 +4570,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4724,11 +4592,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4746,11 +4614,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4768,11 +4636,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4790,11 +4658,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4812,11 +4680,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4834,11 +4702,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4856,11 +4724,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4878,11 +4746,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4900,11 +4768,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4922,11 +4790,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4944,11 +4812,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4966,11 +4834,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4988,11 +4856,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5010,11 +4878,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5032,11 +4900,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5054,11 +4922,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5076,11 +4944,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5098,11 +4966,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5120,11 +4988,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5142,11 +5010,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5164,11 +5032,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5186,11 +5054,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5208,11 +5076,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5230,11 +5098,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5252,11 +5120,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5274,11 +5142,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5296,11 +5164,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5318,11 +5186,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5340,11 +5208,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5362,11 +5230,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5384,11 +5252,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5406,11 +5274,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5428,11 +5296,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5450,11 +5318,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5472,11 +5340,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5494,11 +5362,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5516,11 +5384,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5538,11 +5406,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5560,11 +5428,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5582,11 +5450,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5604,11 +5472,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5626,11 +5494,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5648,11 +5516,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5670,11 +5538,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5692,11 +5560,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5714,11 +5582,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5736,11 +5604,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5758,11 +5626,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5780,11 +5648,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5802,11 +5670,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5824,11 +5692,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5846,11 +5714,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5868,11 +5736,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5890,11 +5758,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5912,11 +5780,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5934,11 +5802,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5956,11 +5824,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5978,11 +5846,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6000,11 +5868,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6022,11 +5890,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6044,11 +5912,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6066,11 +5934,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6088,11 +5956,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6110,11 +5978,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6132,11 +6000,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6154,11 +6022,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6176,11 +6044,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6198,11 +6066,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6220,11 +6088,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6242,11 +6110,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6264,11 +6132,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6286,11 +6154,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6308,11 +6176,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6330,11 +6198,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6352,11 +6220,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6374,11 +6242,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6396,11 +6264,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6418,11 +6286,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6440,11 +6308,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6462,11 +6330,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6484,11 +6352,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6506,11 +6374,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6528,11 +6396,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6550,11 +6418,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6572,11 +6440,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6594,11 +6462,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6616,11 +6484,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6638,11 +6506,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6660,11 +6528,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6682,11 +6550,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6704,11 +6572,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6726,11 +6594,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6748,11 +6616,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6770,11 +6638,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6792,11 +6660,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6814,11 +6682,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6836,11 +6704,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6858,11 +6726,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6880,11 +6748,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6902,11 +6770,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6924,11 +6792,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6946,11 +6814,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6968,11 +6836,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6990,11 +6858,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7012,11 +6880,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7034,11 +6902,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7056,11 +6924,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7078,11 +6946,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7100,11 +6968,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7122,11 +6990,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7144,11 +7012,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7166,11 +7034,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7188,11 +7056,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7210,11 +7078,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7232,11 +7100,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7254,11 +7122,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7276,11 +7144,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7298,11 +7166,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7320,11 +7188,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7342,11 +7210,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7364,11 +7232,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7386,11 +7254,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7408,11 +7276,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7430,11 +7298,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7452,11 +7320,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7474,11 +7342,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7496,11 +7364,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7518,11 +7386,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7540,11 +7408,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7562,11 +7430,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7584,11 +7452,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7606,11 +7474,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7628,11 +7496,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7650,11 +7518,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7672,11 +7540,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7694,11 +7562,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7716,11 +7584,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7738,11 +7606,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7760,11 +7628,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7782,11 +7650,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7804,11 +7672,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7826,11 +7694,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7848,11 +7716,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7870,11 +7738,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7892,11 +7760,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7914,11 +7782,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7936,11 +7804,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7958,11 +7826,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7980,11 +7848,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8002,11 +7870,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8024,11 +7892,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8046,11 +7914,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8068,11 +7936,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8090,11 +7958,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8112,11 +7980,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8134,11 +8002,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8156,11 +8024,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8178,11 +8046,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8200,11 +8068,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8222,11 +8090,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8244,11 +8112,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8266,11 +8134,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8288,11 +8156,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8310,11 +8178,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8332,11 +8200,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8354,11 +8222,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8376,11 +8244,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8398,11 +8266,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8420,11 +8288,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8442,11 +8310,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8464,11 +8332,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8486,11 +8354,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8508,11 +8376,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8530,11 +8398,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8552,11 +8420,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8574,11 +8442,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8596,11 +8464,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8618,11 +8486,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8640,11 +8508,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8662,11 +8530,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8684,11 +8552,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8706,11 +8574,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8728,11 +8596,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8750,11 +8618,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8772,11 +8640,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8794,11 +8662,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8816,11 +8684,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8838,11 +8706,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8860,11 +8728,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8882,11 +8750,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8904,11 +8772,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8926,11 +8794,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8948,11 +8816,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8970,11 +8838,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8992,11 +8860,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9014,11 +8882,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9036,11 +8904,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9058,11 +8926,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9080,11 +8948,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9102,11 +8970,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9124,11 +8992,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9146,11 +9014,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9168,11 +9036,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9190,11 +9058,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9212,11 +9080,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9234,11 +9102,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9256,11 +9124,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9278,11 +9146,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9300,11 +9168,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9322,11 +9190,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9344,11 +9212,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9366,11 +9234,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9388,11 +9256,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9410,11 +9278,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9432,11 +9300,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9454,11 +9322,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9476,11 +9344,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9498,11 +9366,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9520,11 +9388,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9542,11 +9410,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9564,11 +9432,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9586,11 +9454,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9608,11 +9476,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9630,11 +9498,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9652,11 +9520,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9674,11 +9542,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9696,11 +9564,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9718,11 +9586,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9740,11 +9608,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9762,11 +9630,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9784,11 +9652,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9806,11 +9674,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9828,11 +9696,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9850,11 +9718,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9872,11 +9740,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9894,11 +9762,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9916,11 +9784,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9938,11 +9806,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9960,11 +9828,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9982,11 +9850,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10004,11 +9872,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10026,11 +9894,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10048,11 +9916,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10070,11 +9938,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10092,11 +9960,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10114,11 +9982,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10136,11 +10004,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10158,11 +10026,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10180,11 +10048,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10202,11 +10070,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10224,11 +10092,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10246,11 +10114,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10268,11 +10136,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10290,11 +10158,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -10312,11 +10180,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -10334,11 +10202,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -10356,11 +10224,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -10378,11 +10246,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -10400,11 +10268,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -10422,11 +10290,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -10444,11 +10312,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -10466,11 +10334,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -10488,11 +10356,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -10510,11 +10378,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -10532,11 +10400,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -10554,11 +10422,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -10576,11 +10444,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I453" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I453" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J453" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J453" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10598,11 +10466,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10620,11 +10488,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10642,11 +10510,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10664,11 +10532,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10686,11 +10554,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10708,11 +10576,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10730,11 +10598,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10752,11 +10620,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10774,11 +10642,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10796,11 +10664,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10818,11 +10686,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
